--- a/artfynd/A 72780-2021 artfynd.xlsx
+++ b/artfynd/A 72780-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,32 +811,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133592497</v>
+        <v>98723005</v>
       </c>
       <c r="B3" t="n">
-        <v>101422</v>
+        <v>57754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1853</v>
+        <v>102118</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -844,29 +844,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bälter-Svenfallet, Bälter-Svenfallet, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471272</v>
+        <v>471186</v>
       </c>
       <c r="R3" t="n">
-        <v>6768255</v>
+        <v>6768238</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,22 +888,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>1986-08-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>1986-08-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Satt på vägen, fångade insekter. Enligt antboken "i närheten av Östnor"</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,27 +923,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marianne Pasanen-Mortensen</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marianne Pasanen-Mortensen</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133592497</t>
+          <t>https://artportalen.se/Sighting/98723005</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98723005</v>
+        <v>125850915</v>
       </c>
       <c r="B4" t="n">
-        <v>57754</v>
+        <v>56884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,21 +951,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102118</v>
+        <v>208255</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -970,27 +973,36 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Bälter-Svenfallet, Bälter-Svenfallet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471186</v>
+        <v>471305</v>
       </c>
       <c r="R4" t="n">
-        <v>6768238</v>
+        <v>6768243</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,27 +1026,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1986-08-16</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1986-08-16</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Satt på vägen, fångade insekter. Enligt antboken "i närheten av Östnor"</t>
+          <t>Rund om magen - ser ut att vara en dräktig hona.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,161 +1055,23 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Marianne Pasanen-Mortensen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Marianne Pasanen-Mortensen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/98723005</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>125850915</v>
-      </c>
-      <c r="B5" t="n">
-        <v>56884</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>208255</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Skogsödla</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Zootoca vivipara</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Bälter-Svenfallet, Bälter-Svenfallet, Dlr</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>471305</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6768243</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rund om magen - ser ut att vara en dräktig hona.</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Marianne Pasanen-Mortensen</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Marianne Pasanen-Mortensen</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/125850915</t>
         </is>
@@ -1208,7 +1082,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
